--- a/Anudip Lab/Lab3_MD. Tahir Hasan Mondal.xlsx
+++ b/Anudip Lab/Lab3_MD. Tahir Hasan Mondal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1119c1016ca04611/Desktop/Anudip Lab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E299345-E8E3-42D2-A43F-1317048C2058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{5E299345-E8E3-42D2-A43F-1317048C2058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A716C14-F623-4082-BB1B-9C762ED6BBDE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3BDA1EE8-8F9D-43A2-9DED-9B6A1CDC6011}"/>
   </bookViews>
@@ -218,18 +218,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -242,6 +238,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,27 +591,27 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:15" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
     </row>
     <row r="3" spans="3:15" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C3" s="2" t="s">
@@ -778,7 +777,7 @@
         <v>10</v>
       </c>
       <c r="E9" s="3">
-        <v>45330</v>
+        <v>45299</v>
       </c>
       <c r="F9" s="2">
         <v>80</v>
@@ -838,27 +837,27 @@
     </row>
     <row r="14" spans="3:15" ht="12.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="3:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
     </row>
     <row r="16" spans="3:15" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="L16" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -976,27 +975,27 @@
     </row>
     <row r="27" spans="9:15" ht="10" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="9:15" ht="37" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
     </row>
     <row r="29" spans="9:15" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="I29" s="13" t="s">
+      <c r="I29" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J29" s="13" t="s">
+      <c r="J29" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="K29" s="13" t="s">
+      <c r="K29" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="13" t="s">
+      <c r="L29" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1113,30 +1112,30 @@
       </c>
     </row>
     <row r="41" spans="9:17" ht="23.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I41" s="14" t="s">
+      <c r="I41" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="Q41" s="9" t="s">
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="12"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="12"/>
+      <c r="Q41" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="42" spans="9:17" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="I42" s="13" t="s">
+      <c r="I42" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J42" s="13" t="s">
+      <c r="J42" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="13" t="s">
+      <c r="K42" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L42" s="13" t="s">
+      <c r="L42" s="11" t="s">
         <v>6</v>
       </c>
       <c r="Q42" s="2" t="s">
@@ -1186,30 +1185,30 @@
       </c>
     </row>
     <row r="49" spans="9:20" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I49" s="15" t="s">
+      <c r="I49" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="14"/>
-      <c r="Q49" s="10" t="s">
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="N49" s="12"/>
+      <c r="O49" s="12"/>
+      <c r="Q49" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="50" spans="9:20" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="I50" s="13" t="s">
+      <c r="I50" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="J50" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="K50" s="13" t="s">
+      <c r="K50" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L50" s="13" t="s">
+      <c r="L50" s="11" t="s">
         <v>6</v>
       </c>
       <c r="Q50" s="2" t="s">
@@ -1259,57 +1258,48 @@
       </c>
     </row>
     <row r="54" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="7"/>
+      <c r="K54" s="6"/>
     </row>
     <row r="55" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="7"/>
+      <c r="K55" s="6"/>
     </row>
     <row r="56" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="7"/>
+      <c r="K56" s="6"/>
     </row>
     <row r="57" spans="9:20" ht="26.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I57" s="14" t="s">
+      <c r="I57" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="14"/>
-      <c r="O57" s="14"/>
-      <c r="Q57" s="9" t="s">
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
+      <c r="L57" s="12"/>
+      <c r="M57" s="12"/>
+      <c r="N57" s="12"/>
+      <c r="O57" s="12"/>
+      <c r="Q57" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="R57" s="9" t="s">
+      <c r="R57" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="58" spans="9:20" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="I58" s="13" t="s">
+      <c r="I58" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J58" s="13" t="s">
+      <c r="J58" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="13" t="s">
+      <c r="K58" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L58" s="13" t="s">
+      <c r="L58" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="Q58" s="11" t="s">
+      <c r="Q58" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="R58" s="12" t="s">
+      <c r="R58" s="10" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1498,27 +1488,27 @@
       </c>
     </row>
     <row r="70" spans="9:20" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I70" s="15" t="s">
+      <c r="I70" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
-      <c r="N70" s="14"/>
-      <c r="O70" s="14"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="12"/>
+      <c r="N70" s="12"/>
+      <c r="O70" s="12"/>
     </row>
     <row r="71" spans="9:20" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="I71" s="13" t="s">
+      <c r="I71" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J71" s="13" t="s">
+      <c r="J71" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="K71" s="13" t="s">
+      <c r="K71" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L71" s="13" t="s">
+      <c r="L71" s="11" t="s">
         <v>6</v>
       </c>
     </row>
